--- a/artfynd/A 44710-2026 artfynd.xlsx
+++ b/artfynd/A 44710-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>137397907</v>
       </c>
       <c r="B3" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>137397913</v>
       </c>
       <c r="B8" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>137397855</v>
       </c>
       <c r="B12" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
